--- a/table/Datas/#SkydiveConfig.xlsx
+++ b/table/Datas/#SkydiveConfig.xlsx
@@ -962,7 +962,7 @@
         <v>3.1</v>
       </c>
       <c r="AC5" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="AD5" t="n">
         <v>0.35</v>

--- a/table/Datas/#SkydiveConfig.xlsx
+++ b/table/Datas/#SkydiveConfig.xlsx
@@ -965,7 +965,7 @@
         <v>30</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
